--- a/InputData/elec/ETLE/Electricity Technology Logit Exponent.xlsx
+++ b/InputData/elec/ETLE/Electricity Technology Logit Exponent.xlsx
@@ -1,82 +1,72 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junshepard/Library/Containers/com.microsoft.Excel/Data/state-eps-data-repository/template_state/elec/ETLE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\ETLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45FC71F-2E33-1C43-A24D-F421A7292456}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A51EF8-08BF-4631-81FC-8F6F3078DFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" xr2:uid="{9B08635C-C98A-4192-B8F2-5981CE9EC6E6}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="ETLE" sheetId="2" r:id="rId2"/>
+    <sheet name="ETLE-output" sheetId="2" r:id="rId2"/>
+    <sheet name="ETLE-capacity" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+  <si>
+    <t>ETLE Electricity Technology Logit Exponents</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>Sources:</t>
+  </si>
+  <si>
+    <t>None needed.  Handled through calibration.</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>The logit exponents express how large of a cost difference between technology options</t>
+  </si>
+  <si>
+    <t>is required to produce a change in technology selection.  This parameter needs to be</t>
+  </si>
+  <si>
+    <t>obtained via model calibration - e.g. testing a given price intervention with different</t>
+  </si>
+  <si>
+    <t>logit exponent values until it produces a technology choice shift that matches real-world</t>
+  </si>
+  <si>
+    <t>data on technology buyers' behavior.</t>
+  </si>
+  <si>
+    <t>For more on this, see the "Modified Logit" equation description at:</t>
+  </si>
+  <si>
+    <t>https://jgcri.github.io/gcam-doc/choice.html</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless</t>
+  </si>
   <si>
     <t>Exponent</t>
   </si>
   <si>
-    <t>ETLE Electricity Technology Logit Exponent</t>
-  </si>
-  <si>
-    <t>Sources:</t>
-  </si>
-  <si>
-    <t>None needed.  Handled through calibration.</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>The logit exponents express how large of a cost difference between technology options</t>
-  </si>
-  <si>
-    <t>is required to produce a change in technology selection.  This parameter needs to be</t>
-  </si>
-  <si>
-    <t>obtained via model calibration - e.g. testing a given price intervention with different</t>
-  </si>
-  <si>
-    <t>logit exponent values until it produces a technology choice shift that matches real-world</t>
-  </si>
-  <si>
-    <t>data on technology buyers' behavior.</t>
-  </si>
-  <si>
-    <t>For more on this, see the "Modified Logit" equation description at:</t>
-  </si>
-  <si>
-    <t>https://jgcri.github.io/gcam-doc/choice.html</t>
-  </si>
-  <si>
     <t>all electricity sources</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless</t>
   </si>
 </sst>
 </file>
@@ -128,14 +118,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,19 +438,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6422D012-50FD-4D0C-A3BE-19778A6AC198}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4">
-        <v>44308</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -469,42 +458,42 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -515,35 +504,68 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6985D34C-6EF7-4849-ACAF-BBEB94FFD830}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF002060"/>
+    <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" customWidth="1"/>
+    <col min="1" max="1" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2">
+        <v>-90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>